--- a/Incentive_Management_Deck.xlsx
+++ b/Incentive_Management_Deck.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="1. Department" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2. Category &amp; Status" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2. Category View" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="3. City Comparison" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="4. Function &amp; Sub-Function" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="5. BI vs Final" sheetId="6" state="visible" r:id="rId6"/>
@@ -32,7 +32,7 @@
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red]-0.0%;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,6 +71,11 @@
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -181,21 +186,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="11" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -205,11 +210,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -219,14 +224,16 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,6 +453,331 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>Total amount by category (INR)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'2. Category View'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'2. Category View'!$A$5:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'2. Category View'!$C$5:$C$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="55"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E8E8E8"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Average per employee by category (INR)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'2. Category View'!D4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'2. Category View'!$A$5:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'2. Category View'!$D$5:$D$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="55"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E8E8E8"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Verified vs Insufficient Evidence by category (employees)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'2. Category View'!F3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'2. Category View'!$A$5:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'2. Category View'!$F$4:$F$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'2. Category View'!G3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'2. Category View'!$A$5:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'2. Category View'!$G$4:$G$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="55"/>
+        <overlap val="-12"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E8E8E8"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Amount by risk level (INR)</a:t>
             </a:r>
           </a:p>
@@ -461,7 +793,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'2. Category &amp; Status'!C26</f>
+              <f>'2. Category View'!C93</f>
             </strRef>
           </tx>
           <spPr>
@@ -477,12 +809,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2. Category &amp; Status'!$A$27:$A$30</f>
+              <f>'2. Category View'!$A$94:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2. Category &amp; Status'!$C$27:$C$30</f>
+              <f>'2. Category View'!$C$94:$C$97</f>
             </numRef>
           </val>
         </ser>
@@ -531,7 +863,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -628,7 +960,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -725,7 +1057,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -822,7 +1154,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -919,7 +1251,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -1016,7 +1348,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -1141,331 +1473,6 @@
     <legend>
       <legendPos val="r"/>
     </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Variance BI − Final by city (INR)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'5. BI vs Final'!E4</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="EB6834"/>
-            </a:solidFill>
-            <a:ln w="25400">
-              <a:solidFill>
-                <a:srgbClr val="EB6834"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'5. BI vs Final'!$A$5:$A$11</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'5. BI vs Final'!$E$5:$E$11</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="65"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:srgbClr val="E8E8E8"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Apr–Jul total by department — FY2025 vs FY2026</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'6. Apr-Jul by Department'!F3</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
-            </a:solidFill>
-            <a:ln w="25400">
-              <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'6. Apr-Jul by Department'!$A$4:$A$11</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'6. Apr-Jul by Department'!$F$4:$F$11</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'6. Apr-Jul by Department'!K3</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="EB6834"/>
-            </a:solidFill>
-            <a:ln w="25400">
-              <a:solidFill>
-                <a:srgbClr val="EB6834"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'6. Apr-Jul by Department'!$A$4:$A$11</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'6. Apr-Jul by Department'!$K$4:$K$11</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="60"/>
-        <overlap val="-12"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:srgbClr val="E8E8E8"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>YoY variance by department (INR)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'6. Apr-Jul by Department'!L3</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="EB6834"/>
-            </a:solidFill>
-            <a:ln w="25400">
-              <a:solidFill>
-                <a:srgbClr val="EB6834"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'6. Apr-Jul by Department'!$A$4:$A$11</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'6. Apr-Jul by Department'!$L$4:$L$11</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="65"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:srgbClr val="E8E8E8"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -1615,6 +1622,331 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>Variance BI − Final by city (INR)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'5. BI vs Final'!E4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'5. BI vs Final'!$A$5:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'5. BI vs Final'!$E$5:$E$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="65"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E8E8E8"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Apr–Jul total by department — FY2025 vs FY2026</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'6. Apr-Jul by Department'!F3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'6. Apr-Jul by Department'!$A$4:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'6. Apr-Jul by Department'!$F$4:$F$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'6. Apr-Jul by Department'!K3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'6. Apr-Jul by Department'!$A$4:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'6. Apr-Jul by Department'!$K$4:$K$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <overlap val="-12"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E8E8E8"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart22.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>YoY variance by department (INR)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'6. Apr-Jul by Department'!L3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'6. Apr-Jul by Department'!$A$4:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'6. Apr-Jul by Department'!$L$4:$L$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="65"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E8E8E8"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart23.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Apr–Jul total by city — FY2025 vs FY2026</a:t>
             </a:r>
           </a:p>
@@ -1734,7 +2066,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart24.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -2219,7 +2551,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Audited amount by final status</a:t>
+              <a:t>Audited amount by category</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2227,14 +2559,14 @@
     </title>
     <plotArea>
       <barChart>
-        <barDir val="col"/>
+        <barDir val="bar"/>
         <grouping val="clustered"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'2. Category &amp; Status'!C15</f>
+              <f>'2. Category View'!C4</f>
             </strRef>
           </tx>
           <spPr>
@@ -2250,16 +2582,16 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2. Category &amp; Status'!$A$16:$A$22</f>
+              <f>'2. Category View'!$A$5:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2. Category &amp; Status'!$C$16:$C$22</f>
+              <f>'2. Category View'!$C$5:$C$11</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="65"/>
+        <gapWidth val="55"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -2316,7 +2648,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Total incentive by department (INR)</a:t>
+              <a:t>Audited amount by final status</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2324,39 +2656,39 @@
     </title>
     <plotArea>
       <barChart>
-        <barDir val="bar"/>
+        <barDir val="col"/>
         <grouping val="clustered"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'1. Department'!C3</f>
+              <f>'2. Category View'!C82</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="EB6834"/>
             </a:solidFill>
             <a:ln w="25400">
               <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
+                <a:srgbClr val="EB6834"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'1. Department'!$A$4:$A$10</f>
+              <f>'2. Category View'!$A$83:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'1. Department'!$C$4:$C$10</f>
+              <f>'2. Category View'!$C$83:$C$89</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="55"/>
+        <gapWidth val="65"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -2413,7 +2745,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Average per employee by department (INR)</a:t>
+              <a:t>Total incentive by department (INR)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2428,28 +2760,28 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'1. Department'!D3</f>
+              <f>'1. Department'!C3</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="2A78D6"/>
             </a:solidFill>
             <a:ln w="25400">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'1. Department'!$A$4:$A$10</f>
+              <f>'1. Department'!$A$4:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'1. Department'!$D$4:$D$10</f>
+              <f>'1. Department'!$C$4:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -2510,7 +2842,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Amount by category (INR)</a:t>
+              <a:t>Average per employee by department (INR)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2525,28 +2857,28 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'2. Category &amp; Status'!C4</f>
+              <f>'1. Department'!D3</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="EB6834"/>
             </a:solidFill>
             <a:ln w="25400">
               <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
+                <a:srgbClr val="EB6834"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'2. Category &amp; Status'!$A$5:$A$11</f>
+              <f>'1. Department'!$A$4:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2. Category &amp; Status'!$C$5:$C$11</f>
+              <f>'1. Department'!$D$4:$D$11</f>
             </numRef>
           </val>
         </ser>
@@ -2714,7 +3046,7 @@
       <row>131</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3960000"/>
+    <ext cx="7560000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -2724,6 +3056,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>156</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7560000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="7" name="Chart 7"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2785,12 +3139,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3600000"/>
+    <ext cx="7560000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -2807,12 +3161,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>10</col>
       <colOff>0</colOff>
-      <row>24</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3600000"/>
+    <ext cx="7560000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -2822,6 +3176,50 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7560000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>72</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7560000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3386,7 +3784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R81"/>
+  <dimension ref="A1:R91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3493,7 +3891,7 @@
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="6">
-        <f>'2. Category &amp; Status'!E16</f>
+        <f>'2. Category View'!E83</f>
         <v/>
       </c>
       <c r="N5" s="4" t="n"/>
@@ -4456,14 +4854,14 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>AUDIT STATUS</t>
+          <t>CATEGORY — audited amount</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>Final Status</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
@@ -4484,173 +4882,326 @@
     </row>
     <row r="67">
       <c r="A67" s="10">
-        <f>'2. Category &amp; Status'!A16</f>
+        <f>'2. Category View'!A5</f>
         <v/>
       </c>
       <c r="B67" s="16">
-        <f>'2. Category &amp; Status'!B16</f>
+        <f>'2. Category View'!B5</f>
         <v/>
       </c>
       <c r="C67" s="11">
-        <f>'2. Category &amp; Status'!C16</f>
+        <f>'2. Category View'!C5</f>
         <v/>
       </c>
       <c r="D67" s="12">
-        <f>'2. Category &amp; Status'!E16</f>
+        <f>'2. Category View'!E5</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10">
-        <f>'2. Category &amp; Status'!A17</f>
+        <f>'2. Category View'!A6</f>
         <v/>
       </c>
       <c r="B68" s="16">
-        <f>'2. Category &amp; Status'!B17</f>
+        <f>'2. Category View'!B6</f>
         <v/>
       </c>
       <c r="C68" s="11">
-        <f>'2. Category &amp; Status'!C17</f>
+        <f>'2. Category View'!C6</f>
         <v/>
       </c>
       <c r="D68" s="12">
-        <f>'2. Category &amp; Status'!E17</f>
+        <f>'2. Category View'!E6</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10">
-        <f>'2. Category &amp; Status'!A18</f>
+        <f>'2. Category View'!A7</f>
         <v/>
       </c>
       <c r="B69" s="16">
-        <f>'2. Category &amp; Status'!B18</f>
+        <f>'2. Category View'!B7</f>
         <v/>
       </c>
       <c r="C69" s="11">
-        <f>'2. Category &amp; Status'!C18</f>
+        <f>'2. Category View'!C7</f>
         <v/>
       </c>
       <c r="D69" s="12">
-        <f>'2. Category &amp; Status'!E18</f>
+        <f>'2. Category View'!E7</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10">
-        <f>'2. Category &amp; Status'!A19</f>
+        <f>'2. Category View'!A8</f>
         <v/>
       </c>
       <c r="B70" s="16">
-        <f>'2. Category &amp; Status'!B19</f>
+        <f>'2. Category View'!B8</f>
         <v/>
       </c>
       <c r="C70" s="11">
-        <f>'2. Category &amp; Status'!C19</f>
+        <f>'2. Category View'!C8</f>
         <v/>
       </c>
       <c r="D70" s="12">
-        <f>'2. Category &amp; Status'!E19</f>
+        <f>'2. Category View'!E8</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10">
-        <f>'2. Category &amp; Status'!A20</f>
+        <f>'2. Category View'!A9</f>
         <v/>
       </c>
       <c r="B71" s="16">
-        <f>'2. Category &amp; Status'!B20</f>
+        <f>'2. Category View'!B9</f>
         <v/>
       </c>
       <c r="C71" s="11">
-        <f>'2. Category &amp; Status'!C20</f>
+        <f>'2. Category View'!C9</f>
         <v/>
       </c>
       <c r="D71" s="12">
-        <f>'2. Category &amp; Status'!E20</f>
+        <f>'2. Category View'!E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10">
+        <f>'2. Category View'!A10</f>
+        <v/>
+      </c>
+      <c r="B72" s="16">
+        <f>'2. Category View'!B10</f>
+        <v/>
+      </c>
+      <c r="C72" s="11">
+        <f>'2. Category View'!C10</f>
+        <v/>
+      </c>
+      <c r="D72" s="12">
+        <f>'2. Category View'!E10</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
+      <c r="A73" s="10">
+        <f>'2. Category View'!A11</f>
+        <v/>
+      </c>
+      <c r="B73" s="16">
+        <f>'2. Category View'!B11</f>
+        <v/>
+      </c>
+      <c r="C73" s="11">
+        <f>'2. Category View'!C11</f>
+        <v/>
+      </c>
+      <c r="D73" s="12">
+        <f>'2. Category View'!E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>AUDIT STATUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>Final Status</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>Employees</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>% of Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10">
+        <f>'2. Category View'!A83</f>
+        <v/>
+      </c>
+      <c r="B77" s="16">
+        <f>'2. Category View'!B83</f>
+        <v/>
+      </c>
+      <c r="C77" s="11">
+        <f>'2. Category View'!C83</f>
+        <v/>
+      </c>
+      <c r="D77" s="12">
+        <f>'2. Category View'!E83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10">
+        <f>'2. Category View'!A84</f>
+        <v/>
+      </c>
+      <c r="B78" s="16">
+        <f>'2. Category View'!B84</f>
+        <v/>
+      </c>
+      <c r="C78" s="11">
+        <f>'2. Category View'!C84</f>
+        <v/>
+      </c>
+      <c r="D78" s="12">
+        <f>'2. Category View'!E84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10">
+        <f>'2. Category View'!A85</f>
+        <v/>
+      </c>
+      <c r="B79" s="16">
+        <f>'2. Category View'!B85</f>
+        <v/>
+      </c>
+      <c r="C79" s="11">
+        <f>'2. Category View'!C85</f>
+        <v/>
+      </c>
+      <c r="D79" s="12">
+        <f>'2. Category View'!E85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10">
+        <f>'2. Category View'!A86</f>
+        <v/>
+      </c>
+      <c r="B80" s="16">
+        <f>'2. Category View'!B86</f>
+        <v/>
+      </c>
+      <c r="C80" s="11">
+        <f>'2. Category View'!C86</f>
+        <v/>
+      </c>
+      <c r="D80" s="12">
+        <f>'2. Category View'!E86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10">
+        <f>'2. Category View'!A87</f>
+        <v/>
+      </c>
+      <c r="B81" s="16">
+        <f>'2. Category View'!B87</f>
+        <v/>
+      </c>
+      <c r="C81" s="11">
+        <f>'2. Category View'!C87</f>
+        <v/>
+      </c>
+      <c r="D81" s="12">
+        <f>'2. Category View'!E87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
         <is>
           <t>BI vs FINAL AMOUNT</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="9" t="inlineStr">
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="9" t="inlineStr">
         <is>
           <t>Measure</t>
         </is>
       </c>
-      <c r="B74" s="9" t="inlineStr">
+      <c r="B84" s="9" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="10" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>Rows with BI computed (328)</t>
         </is>
       </c>
-      <c r="B75" s="11">
+      <c r="B85" s="11">
         <f>'5. BI vs Final'!C12</f>
         <v/>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="10" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  BI amount on those rows</t>
         </is>
       </c>
-      <c r="B76" s="11">
+      <c r="B86" s="11">
         <f>'5. BI vs Final'!D12</f>
         <v/>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Genuine gap (BI − Final)</t>
         </is>
       </c>
-      <c r="B77" s="11">
+      <c r="B87" s="11">
         <f>'5. BI vs Final'!E12</f>
         <v/>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="10" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>Rows with NO BI (618) — evidence gap</t>
         </is>
       </c>
-      <c r="B78" s="11">
+      <c r="B88" s="11">
         <f>'5. BI vs Final'!C23</f>
         <v/>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="17" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="17" t="inlineStr">
         <is>
           <t>Reading notes:  (1) April–July only, both years.  (2) City on the MOM sheets is mapped from the audit file by Employee ID; employees absent from it are grouped as "Not in audit file".  (3) BI = 0 means BI was not computed for that row, not that BI is zero — so the headline risk figure overstates true overpayment.  (4) Function / Sub-Function exist only in the audit file.</t>
         </is>
       </c>
     </row>
-    <row r="80"/>
-    <row r="81"/>
+    <row r="90"/>
+    <row r="91"/>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="29">
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="D5:F6"/>
-    <mergeCell ref="A73:B73"/>
     <mergeCell ref="P5:R6"/>
-    <mergeCell ref="A79:H81"/>
     <mergeCell ref="A52:D52"/>
     <mergeCell ref="J5:L6"/>
     <mergeCell ref="M7:O7"/>
@@ -4667,12 +5218,15 @@
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="M4:O4"/>
+    <mergeCell ref="A89:H91"/>
     <mergeCell ref="A65:D65"/>
     <mergeCell ref="P4:R4"/>
+    <mergeCell ref="A75:D75"/>
     <mergeCell ref="A5:C6"/>
     <mergeCell ref="G5:I6"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="G7:I7"/>
+    <mergeCell ref="A83:B83"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11898,7 +12452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11986,7 +12540,7 @@
         <v/>
       </c>
       <c r="E4" s="21">
-        <f>IF($C$11=0,"",C4/$C$11)</f>
+        <f>IF($C$12=0,"",C4/$C$12)</f>
         <v/>
       </c>
       <c r="F4" s="19">
@@ -12021,7 +12575,7 @@
         <v/>
       </c>
       <c r="E5" s="21">
-        <f>IF($C$11=0,"",C5/$C$11)</f>
+        <f>IF($C$12=0,"",C5/$C$12)</f>
         <v/>
       </c>
       <c r="F5" s="19">
@@ -12056,7 +12610,7 @@
         <v/>
       </c>
       <c r="E6" s="21">
-        <f>IF($C$11=0,"",C6/$C$11)</f>
+        <f>IF($C$12=0,"",C6/$C$12)</f>
         <v/>
       </c>
       <c r="F6" s="19">
@@ -12091,7 +12645,7 @@
         <v/>
       </c>
       <c r="E7" s="21">
-        <f>IF($C$11=0,"",C7/$C$11)</f>
+        <f>IF($C$12=0,"",C7/$C$12)</f>
         <v/>
       </c>
       <c r="F7" s="19">
@@ -12126,7 +12680,7 @@
         <v/>
       </c>
       <c r="E8" s="21">
-        <f>IF($C$11=0,"",C8/$C$11)</f>
+        <f>IF($C$12=0,"",C8/$C$12)</f>
         <v/>
       </c>
       <c r="F8" s="19">
@@ -12145,7 +12699,7 @@
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>Supporting Functions</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="B9" s="19">
@@ -12161,7 +12715,7 @@
         <v/>
       </c>
       <c r="E9" s="21">
-        <f>IF($C$11=0,"",C9/$C$11)</f>
+        <f>IF($C$12=0,"",C9/$C$12)</f>
         <v/>
       </c>
       <c r="F9" s="19">
@@ -12180,7 +12734,7 @@
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Supporting Functions</t>
         </is>
       </c>
       <c r="B10" s="19">
@@ -12196,7 +12750,7 @@
         <v/>
       </c>
       <c r="E10" s="21">
-        <f>IF($C$11=0,"",C10/$C$11)</f>
+        <f>IF($C$12=0,"",C10/$C$12)</f>
         <v/>
       </c>
       <c r="F10" s="19">
@@ -12213,34 +12767,69 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B11" s="19">
+        <f>COUNTIF('Audit Detail'!$D$4:$D$949,$A11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="20">
+        <f>SUMIF('Audit Detail'!$D$4:$D$949,$A11,'Audit Detail'!$J$4:$J$949)</f>
+        <v/>
+      </c>
+      <c r="D11" s="20">
+        <f>IF(B11=0,0,C11/B11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="21">
+        <f>IF($C$12=0,"",C11/$C$12)</f>
+        <v/>
+      </c>
+      <c r="F11" s="19">
+        <f>COUNTIFS('Audit Detail'!$D$4:$D$949,$A11,'Audit Detail'!$H$4:$H$949,"Verified")</f>
+        <v/>
+      </c>
+      <c r="G11" s="19">
+        <f>COUNTIFS('Audit Detail'!$D$4:$D$949,$A11,'Audit Detail'!$H$4:$H$949,"Insufficient Evidence")</f>
+        <v/>
+      </c>
+      <c r="H11" s="19">
+        <f>COUNTIFS('Audit Detail'!$D$4:$D$949,$A11,'Audit Detail'!$I$4:$I$949,"High")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" s="23">
-        <f>SUM(B4:B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="24">
-        <f>SUM(C4:C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="24">
-        <f>IF(B11=0,0,C11/B11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="22" t="n"/>
-      <c r="F11" s="23">
-        <f>SUM(F4:F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="23">
-        <f>SUM(G4:G10)</f>
-        <v/>
-      </c>
-      <c r="H11" s="23">
-        <f>SUM(H4:H10)</f>
+      <c r="B12" s="23">
+        <f>SUM(B4:B11)</f>
+        <v/>
+      </c>
+      <c r="C12" s="24">
+        <f>SUM(C4:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>IF(B12=0,0,C12/B12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="23">
+        <f>SUM(F4:F11)</f>
+        <v/>
+      </c>
+      <c r="G12" s="23">
+        <f>SUM(G4:G11)</f>
+        <v/>
+      </c>
+      <c r="H12" s="23">
+        <f>SUM(H4:H11)</f>
         <v/>
       </c>
     </row>
@@ -12260,37 +12849,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:I98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>CATEGORY, STATUS &amp; RISK VIEW</t>
+          <t>CATEGORY VIEW</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total amount, average and employee count across each classification.</t>
+          <t>How every rupee was classified, and what each classification is worth. Category is the audit judgement on whether the payout could be reproduced from a formula.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>BY CATEGORY</t>
+          <t>A. CATEGORY SUMMARY</t>
         </is>
       </c>
     </row>
@@ -12616,195 +13206,261 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>BY FINAL STATUS</t>
+          <t>B. CATEGORY — BI COVERAGE &amp; GAP  (BI = 0 means BI was not computed)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Final Status</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>Rows with BI</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Total Amount</t>
+          <t>BI Amount</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Avg per Employee</t>
+          <t>Final on those rows</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>% of Total</t>
+          <t>Gap (BI − Final)</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Rows without BI</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Amount without BI</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Formula Based</t>
         </is>
       </c>
       <c r="B16" s="19">
-        <f>COUNTIF('Audit Detail'!$H$4:$H$949,$A16)</f>
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A16,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
         <v/>
       </c>
       <c r="C16" s="20">
-        <f>SUMIF('Audit Detail'!$H$4:$H$949,$A16,'Audit Detail'!$J$4:$J$949)</f>
+        <f>SUMIFS('Audit Detail'!$K$4:$K$949,'Audit Detail'!$G$4:$G$949,$A16,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
         <v/>
       </c>
       <c r="D16" s="20">
-        <f>IF(B16=0,0,C16/B16)</f>
-        <v/>
-      </c>
-      <c r="E16" s="21">
-        <f>IF($C$23=0,"",C16/$C$23)</f>
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A16,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="E16" s="20">
+        <f>C16-D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="19">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A16,'Audit Detail'!$K$4:$K$949,"=0")</f>
+        <v/>
+      </c>
+      <c r="G16" s="20">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A16,'Audit Detail'!$K$4:$K$949,"=0")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>Insufficient Evidence</t>
+          <t>Subjective / Fixed</t>
         </is>
       </c>
       <c r="B17" s="19">
-        <f>COUNTIF('Audit Detail'!$H$4:$H$949,$A17)</f>
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A17,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
         <v/>
       </c>
       <c r="C17" s="20">
-        <f>SUMIF('Audit Detail'!$H$4:$H$949,$A17,'Audit Detail'!$J$4:$J$949)</f>
+        <f>SUMIFS('Audit Detail'!$K$4:$K$949,'Audit Detail'!$G$4:$G$949,$A17,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
         <v/>
       </c>
       <c r="D17" s="20">
-        <f>IF(B17=0,0,C17/B17)</f>
-        <v/>
-      </c>
-      <c r="E17" s="21">
-        <f>IF($C$23=0,"",C17/$C$23)</f>
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A17,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="E17" s="20">
+        <f>C17-D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="19">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A17,'Audit Detail'!$K$4:$K$949,"=0")</f>
+        <v/>
+      </c>
+      <c r="G17" s="20">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A17,'Audit Detail'!$K$4:$K$949,"=0")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>Mismatch — Overpaid</t>
+          <t>Subjective / Evidence Missing</t>
         </is>
       </c>
       <c r="B18" s="19">
-        <f>COUNTIF('Audit Detail'!$H$4:$H$949,$A18)</f>
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A18,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
         <v/>
       </c>
       <c r="C18" s="20">
-        <f>SUMIF('Audit Detail'!$H$4:$H$949,$A18,'Audit Detail'!$J$4:$J$949)</f>
+        <f>SUMIFS('Audit Detail'!$K$4:$K$949,'Audit Detail'!$G$4:$G$949,$A18,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
         <v/>
       </c>
       <c r="D18" s="20">
-        <f>IF(B18=0,0,C18/B18)</f>
-        <v/>
-      </c>
-      <c r="E18" s="21">
-        <f>IF($C$23=0,"",C18/$C$23)</f>
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A18,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="E18" s="20">
+        <f>C18-D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="19">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A18,'Audit Detail'!$K$4:$K$949,"=0")</f>
+        <v/>
+      </c>
+      <c r="G18" s="20">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A18,'Audit Detail'!$K$4:$K$949,"=0")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>Mismatch — Underpaid</t>
+          <t>Part Formula + Subjective/Incomplete Evidence</t>
         </is>
       </c>
       <c r="B19" s="19">
-        <f>COUNTIF('Audit Detail'!$H$4:$H$949,$A19)</f>
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A19,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
         <v/>
       </c>
       <c r="C19" s="20">
-        <f>SUMIF('Audit Detail'!$H$4:$H$949,$A19,'Audit Detail'!$J$4:$J$949)</f>
+        <f>SUMIFS('Audit Detail'!$K$4:$K$949,'Audit Detail'!$G$4:$G$949,$A19,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
         <v/>
       </c>
       <c r="D19" s="20">
-        <f>IF(B19=0,0,C19/B19)</f>
-        <v/>
-      </c>
-      <c r="E19" s="21">
-        <f>IF($C$23=0,"",C19/$C$23)</f>
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A19,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="E19" s="20">
+        <f>C19-D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="19">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A19,'Audit Detail'!$K$4:$K$949,"=0")</f>
+        <v/>
+      </c>
+      <c r="G19" s="20">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A19,'Audit Detail'!$K$4:$K$949,"=0")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Subjective</t>
         </is>
       </c>
       <c r="B20" s="19">
-        <f>COUNTIF('Audit Detail'!$H$4:$H$949,$A20)</f>
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A20,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
         <v/>
       </c>
       <c r="C20" s="20">
-        <f>SUMIF('Audit Detail'!$H$4:$H$949,$A20,'Audit Detail'!$J$4:$J$949)</f>
+        <f>SUMIFS('Audit Detail'!$K$4:$K$949,'Audit Detail'!$G$4:$G$949,$A20,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
         <v/>
       </c>
       <c r="D20" s="20">
-        <f>IF(B20=0,0,C20/B20)</f>
-        <v/>
-      </c>
-      <c r="E20" s="21">
-        <f>IF($C$23=0,"",C20/$C$23)</f>
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A20,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="E20" s="20">
+        <f>C20-D20</f>
+        <v/>
+      </c>
+      <c r="F20" s="19">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A20,'Audit Detail'!$K$4:$K$949,"=0")</f>
+        <v/>
+      </c>
+      <c r="G20" s="20">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A20,'Audit Detail'!$K$4:$K$949,"=0")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>Insufficient Evidence — No Overpayment</t>
+          <t>Part Formula + Manual/Fixed Component</t>
         </is>
       </c>
       <c r="B21" s="19">
-        <f>COUNTIF('Audit Detail'!$H$4:$H$949,$A21)</f>
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A21,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
         <v/>
       </c>
       <c r="C21" s="20">
-        <f>SUMIF('Audit Detail'!$H$4:$H$949,$A21,'Audit Detail'!$J$4:$J$949)</f>
+        <f>SUMIFS('Audit Detail'!$K$4:$K$949,'Audit Detail'!$G$4:$G$949,$A21,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
         <v/>
       </c>
       <c r="D21" s="20">
-        <f>IF(B21=0,0,C21/B21)</f>
-        <v/>
-      </c>
-      <c r="E21" s="21">
-        <f>IF($C$23=0,"",C21/$C$23)</f>
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A21,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="E21" s="20">
+        <f>C21-D21</f>
+        <v/>
+      </c>
+      <c r="F21" s="19">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A21,'Audit Detail'!$K$4:$K$949,"=0")</f>
+        <v/>
+      </c>
+      <c r="G21" s="20">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A21,'Audit Detail'!$K$4:$K$949,"=0")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>Mismatch — Overpaid / Evidence Incomplete</t>
+          <t>Insufficient Evidence</t>
         </is>
       </c>
       <c r="B22" s="19">
-        <f>COUNTIF('Audit Detail'!$H$4:$H$949,$A22)</f>
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A22,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
         <v/>
       </c>
       <c r="C22" s="20">
-        <f>SUMIF('Audit Detail'!$H$4:$H$949,$A22,'Audit Detail'!$J$4:$J$949)</f>
+        <f>SUMIFS('Audit Detail'!$K$4:$K$949,'Audit Detail'!$G$4:$G$949,$A22,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
         <v/>
       </c>
       <c r="D22" s="20">
-        <f>IF(B22=0,0,C22/B22)</f>
-        <v/>
-      </c>
-      <c r="E22" s="21">
-        <f>IF($C$23=0,"",C22/$C$23)</f>
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A22,'Audit Detail'!$K$4:$K$949,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="E22" s="20">
+        <f>C22-D22</f>
+        <v/>
+      </c>
+      <c r="F22" s="19">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A22,'Audit Detail'!$K$4:$K$949,"=0")</f>
+        <v/>
+      </c>
+      <c r="G22" s="20">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A22,'Audit Detail'!$K$4:$K$949,"=0")</f>
         <v/>
       </c>
     </row>
@@ -12822,163 +13478,2116 @@
         <f>SUM(C16:C22)</f>
         <v/>
       </c>
-      <c r="D23" s="25">
-        <f>IF(B23=0,0,C23/B23)</f>
+      <c r="D23" s="24">
+        <f>SUM(D16:D22)</f>
+        <v/>
+      </c>
+      <c r="E23" s="24">
+        <f>SUM(E16:E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="23">
+        <f>SUM(F16:F22)</f>
+        <v/>
+      </c>
+      <c r="G23" s="24">
+        <f>SUM(G16:G22)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>BY RISK LEVEL</t>
+          <t>C. CATEGORY × FINAL STATUS  (employees)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Insufficient Evidence</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Mismatch — Overpaid</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Mismatch — Underpaid</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>Insufficient Evidence — No Overpayment</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>Mismatch — Overpaid / Evidence Incomplete</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Formula Based</t>
+        </is>
+      </c>
+      <c r="B27" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A27,'Audit Detail'!$H$4:$H$949,"Verified")</f>
+        <v/>
+      </c>
+      <c r="C27" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A27,'Audit Detail'!$H$4:$H$949,"Insufficient Evidence")</f>
+        <v/>
+      </c>
+      <c r="D27" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A27,'Audit Detail'!$H$4:$H$949,"Mismatch — Overpaid")</f>
+        <v/>
+      </c>
+      <c r="E27" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A27,'Audit Detail'!$H$4:$H$949,"Mismatch — Underpaid")</f>
+        <v/>
+      </c>
+      <c r="F27" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A27,'Audit Detail'!$H$4:$H$949,"Mismatch")</f>
+        <v/>
+      </c>
+      <c r="G27" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A27,'Audit Detail'!$H$4:$H$949,"Insufficient Evidence — No Overpayment")</f>
+        <v/>
+      </c>
+      <c r="H27" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A27,'Audit Detail'!$H$4:$H$949,"Mismatch — Overpaid / Evidence Incomplete")</f>
+        <v/>
+      </c>
+      <c r="I27" s="25">
+        <f>SUM(B27:H27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Subjective / Fixed</t>
+        </is>
+      </c>
+      <c r="B28" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A28,'Audit Detail'!$H$4:$H$949,"Verified")</f>
+        <v/>
+      </c>
+      <c r="C28" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A28,'Audit Detail'!$H$4:$H$949,"Insufficient Evidence")</f>
+        <v/>
+      </c>
+      <c r="D28" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A28,'Audit Detail'!$H$4:$H$949,"Mismatch — Overpaid")</f>
+        <v/>
+      </c>
+      <c r="E28" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A28,'Audit Detail'!$H$4:$H$949,"Mismatch — Underpaid")</f>
+        <v/>
+      </c>
+      <c r="F28" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A28,'Audit Detail'!$H$4:$H$949,"Mismatch")</f>
+        <v/>
+      </c>
+      <c r="G28" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A28,'Audit Detail'!$H$4:$H$949,"Insufficient Evidence — No Overpayment")</f>
+        <v/>
+      </c>
+      <c r="H28" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A28,'Audit Detail'!$H$4:$H$949,"Mismatch — Overpaid / Evidence Incomplete")</f>
+        <v/>
+      </c>
+      <c r="I28" s="25">
+        <f>SUM(B28:H28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Subjective / Evidence Missing</t>
+        </is>
+      </c>
+      <c r="B29" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A29,'Audit Detail'!$H$4:$H$949,"Verified")</f>
+        <v/>
+      </c>
+      <c r="C29" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A29,'Audit Detail'!$H$4:$H$949,"Insufficient Evidence")</f>
+        <v/>
+      </c>
+      <c r="D29" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A29,'Audit Detail'!$H$4:$H$949,"Mismatch — Overpaid")</f>
+        <v/>
+      </c>
+      <c r="E29" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A29,'Audit Detail'!$H$4:$H$949,"Mismatch — Underpaid")</f>
+        <v/>
+      </c>
+      <c r="F29" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A29,'Audit Detail'!$H$4:$H$949,"Mismatch")</f>
+        <v/>
+      </c>
+      <c r="G29" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A29,'Audit Detail'!$H$4:$H$949,"Insufficient Evidence — No Overpayment")</f>
+        <v/>
+      </c>
+      <c r="H29" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A29,'Audit Detail'!$H$4:$H$949,"Mismatch — Overpaid / Evidence Incomplete")</f>
+        <v/>
+      </c>
+      <c r="I29" s="25">
+        <f>SUM(B29:H29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Part Formula + Subjective/Incomplete Evidence</t>
+        </is>
+      </c>
+      <c r="B30" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A30,'Audit Detail'!$H$4:$H$949,"Verified")</f>
+        <v/>
+      </c>
+      <c r="C30" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A30,'Audit Detail'!$H$4:$H$949,"Insufficient Evidence")</f>
+        <v/>
+      </c>
+      <c r="D30" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A30,'Audit Detail'!$H$4:$H$949,"Mismatch — Overpaid")</f>
+        <v/>
+      </c>
+      <c r="E30" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A30,'Audit Detail'!$H$4:$H$949,"Mismatch — Underpaid")</f>
+        <v/>
+      </c>
+      <c r="F30" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A30,'Audit Detail'!$H$4:$H$949,"Mismatch")</f>
+        <v/>
+      </c>
+      <c r="G30" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A30,'Audit Detail'!$H$4:$H$949,"Insufficient Evidence — No Overpayment")</f>
+        <v/>
+      </c>
+      <c r="H30" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A30,'Audit Detail'!$H$4:$H$949,"Mismatch — Overpaid / Evidence Incomplete")</f>
+        <v/>
+      </c>
+      <c r="I30" s="25">
+        <f>SUM(B30:H30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Subjective</t>
+        </is>
+      </c>
+      <c r="B31" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A31,'Audit Detail'!$H$4:$H$949,"Verified")</f>
+        <v/>
+      </c>
+      <c r="C31" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A31,'Audit Detail'!$H$4:$H$949,"Insufficient Evidence")</f>
+        <v/>
+      </c>
+      <c r="D31" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A31,'Audit Detail'!$H$4:$H$949,"Mismatch — Overpaid")</f>
+        <v/>
+      </c>
+      <c r="E31" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A31,'Audit Detail'!$H$4:$H$949,"Mismatch — Underpaid")</f>
+        <v/>
+      </c>
+      <c r="F31" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A31,'Audit Detail'!$H$4:$H$949,"Mismatch")</f>
+        <v/>
+      </c>
+      <c r="G31" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A31,'Audit Detail'!$H$4:$H$949,"Insufficient Evidence — No Overpayment")</f>
+        <v/>
+      </c>
+      <c r="H31" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A31,'Audit Detail'!$H$4:$H$949,"Mismatch — Overpaid / Evidence Incomplete")</f>
+        <v/>
+      </c>
+      <c r="I31" s="25">
+        <f>SUM(B31:H31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Part Formula + Manual/Fixed Component</t>
+        </is>
+      </c>
+      <c r="B32" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A32,'Audit Detail'!$H$4:$H$949,"Verified")</f>
+        <v/>
+      </c>
+      <c r="C32" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A32,'Audit Detail'!$H$4:$H$949,"Insufficient Evidence")</f>
+        <v/>
+      </c>
+      <c r="D32" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A32,'Audit Detail'!$H$4:$H$949,"Mismatch — Overpaid")</f>
+        <v/>
+      </c>
+      <c r="E32" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A32,'Audit Detail'!$H$4:$H$949,"Mismatch — Underpaid")</f>
+        <v/>
+      </c>
+      <c r="F32" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A32,'Audit Detail'!$H$4:$H$949,"Mismatch")</f>
+        <v/>
+      </c>
+      <c r="G32" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A32,'Audit Detail'!$H$4:$H$949,"Insufficient Evidence — No Overpayment")</f>
+        <v/>
+      </c>
+      <c r="H32" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A32,'Audit Detail'!$H$4:$H$949,"Mismatch — Overpaid / Evidence Incomplete")</f>
+        <v/>
+      </c>
+      <c r="I32" s="25">
+        <f>SUM(B32:H32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Insufficient Evidence</t>
+        </is>
+      </c>
+      <c r="B33" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A33,'Audit Detail'!$H$4:$H$949,"Verified")</f>
+        <v/>
+      </c>
+      <c r="C33" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A33,'Audit Detail'!$H$4:$H$949,"Insufficient Evidence")</f>
+        <v/>
+      </c>
+      <c r="D33" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A33,'Audit Detail'!$H$4:$H$949,"Mismatch — Overpaid")</f>
+        <v/>
+      </c>
+      <c r="E33" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A33,'Audit Detail'!$H$4:$H$949,"Mismatch — Underpaid")</f>
+        <v/>
+      </c>
+      <c r="F33" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A33,'Audit Detail'!$H$4:$H$949,"Mismatch")</f>
+        <v/>
+      </c>
+      <c r="G33" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A33,'Audit Detail'!$H$4:$H$949,"Insufficient Evidence — No Overpayment")</f>
+        <v/>
+      </c>
+      <c r="H33" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A33,'Audit Detail'!$H$4:$H$949,"Mismatch — Overpaid / Evidence Incomplete")</f>
+        <v/>
+      </c>
+      <c r="I33" s="25">
+        <f>SUM(B33:H33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B34" s="23">
+        <f>SUM(B27:B33)</f>
+        <v/>
+      </c>
+      <c r="C34" s="23">
+        <f>SUM(C27:C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="23">
+        <f>SUM(D27:D33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="23">
+        <f>SUM(E27:E33)</f>
+        <v/>
+      </c>
+      <c r="F34" s="23">
+        <f>SUM(F27:F33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="23">
+        <f>SUM(G27:G33)</f>
+        <v/>
+      </c>
+      <c r="H34" s="23">
+        <f>SUM(H27:H33)</f>
+        <v/>
+      </c>
+      <c r="I34" s="23">
+        <f>SUM(I27:I33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>D. CATEGORY × RISK LEVEL  (employees)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>No Risk</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Formula Based</t>
+        </is>
+      </c>
+      <c r="B38" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A38,'Audit Detail'!$I$4:$I$949,"No Risk")</f>
+        <v/>
+      </c>
+      <c r="C38" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A38,'Audit Detail'!$I$4:$I$949,"Low")</f>
+        <v/>
+      </c>
+      <c r="D38" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A38,'Audit Detail'!$I$4:$I$949,"Medium")</f>
+        <v/>
+      </c>
+      <c r="E38" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A38,'Audit Detail'!$I$4:$I$949,"High")</f>
+        <v/>
+      </c>
+      <c r="F38" s="25">
+        <f>SUM(B38:E38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>Subjective / Fixed</t>
+        </is>
+      </c>
+      <c r="B39" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A39,'Audit Detail'!$I$4:$I$949,"No Risk")</f>
+        <v/>
+      </c>
+      <c r="C39" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A39,'Audit Detail'!$I$4:$I$949,"Low")</f>
+        <v/>
+      </c>
+      <c r="D39" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A39,'Audit Detail'!$I$4:$I$949,"Medium")</f>
+        <v/>
+      </c>
+      <c r="E39" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A39,'Audit Detail'!$I$4:$I$949,"High")</f>
+        <v/>
+      </c>
+      <c r="F39" s="25">
+        <f>SUM(B39:E39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Subjective / Evidence Missing</t>
+        </is>
+      </c>
+      <c r="B40" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A40,'Audit Detail'!$I$4:$I$949,"No Risk")</f>
+        <v/>
+      </c>
+      <c r="C40" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A40,'Audit Detail'!$I$4:$I$949,"Low")</f>
+        <v/>
+      </c>
+      <c r="D40" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A40,'Audit Detail'!$I$4:$I$949,"Medium")</f>
+        <v/>
+      </c>
+      <c r="E40" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A40,'Audit Detail'!$I$4:$I$949,"High")</f>
+        <v/>
+      </c>
+      <c r="F40" s="25">
+        <f>SUM(B40:E40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>Part Formula + Subjective/Incomplete Evidence</t>
+        </is>
+      </c>
+      <c r="B41" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A41,'Audit Detail'!$I$4:$I$949,"No Risk")</f>
+        <v/>
+      </c>
+      <c r="C41" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A41,'Audit Detail'!$I$4:$I$949,"Low")</f>
+        <v/>
+      </c>
+      <c r="D41" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A41,'Audit Detail'!$I$4:$I$949,"Medium")</f>
+        <v/>
+      </c>
+      <c r="E41" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A41,'Audit Detail'!$I$4:$I$949,"High")</f>
+        <v/>
+      </c>
+      <c r="F41" s="25">
+        <f>SUM(B41:E41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>Subjective</t>
+        </is>
+      </c>
+      <c r="B42" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A42,'Audit Detail'!$I$4:$I$949,"No Risk")</f>
+        <v/>
+      </c>
+      <c r="C42" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A42,'Audit Detail'!$I$4:$I$949,"Low")</f>
+        <v/>
+      </c>
+      <c r="D42" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A42,'Audit Detail'!$I$4:$I$949,"Medium")</f>
+        <v/>
+      </c>
+      <c r="E42" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A42,'Audit Detail'!$I$4:$I$949,"High")</f>
+        <v/>
+      </c>
+      <c r="F42" s="25">
+        <f>SUM(B42:E42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>Part Formula + Manual/Fixed Component</t>
+        </is>
+      </c>
+      <c r="B43" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A43,'Audit Detail'!$I$4:$I$949,"No Risk")</f>
+        <v/>
+      </c>
+      <c r="C43" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A43,'Audit Detail'!$I$4:$I$949,"Low")</f>
+        <v/>
+      </c>
+      <c r="D43" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A43,'Audit Detail'!$I$4:$I$949,"Medium")</f>
+        <v/>
+      </c>
+      <c r="E43" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A43,'Audit Detail'!$I$4:$I$949,"High")</f>
+        <v/>
+      </c>
+      <c r="F43" s="25">
+        <f>SUM(B43:E43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>Insufficient Evidence</t>
+        </is>
+      </c>
+      <c r="B44" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A44,'Audit Detail'!$I$4:$I$949,"No Risk")</f>
+        <v/>
+      </c>
+      <c r="C44" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A44,'Audit Detail'!$I$4:$I$949,"Low")</f>
+        <v/>
+      </c>
+      <c r="D44" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A44,'Audit Detail'!$I$4:$I$949,"Medium")</f>
+        <v/>
+      </c>
+      <c r="E44" s="16">
+        <f>COUNTIFS('Audit Detail'!$G$4:$G$949,$A44,'Audit Detail'!$I$4:$I$949,"High")</f>
+        <v/>
+      </c>
+      <c r="F44" s="25">
+        <f>SUM(B44:E44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B45" s="23">
+        <f>SUM(B38:B44)</f>
+        <v/>
+      </c>
+      <c r="C45" s="23">
+        <f>SUM(C38:C44)</f>
+        <v/>
+      </c>
+      <c r="D45" s="23">
+        <f>SUM(D38:D44)</f>
+        <v/>
+      </c>
+      <c r="E45" s="23">
+        <f>SUM(E38:E44)</f>
+        <v/>
+      </c>
+      <c r="F45" s="23">
+        <f>SUM(F38:F44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>E. CATEGORY × CITY  (amount)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>Delhi NCR</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>Formula Based</t>
+        </is>
+      </c>
+      <c r="B49" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A49,'Audit Detail'!$A$4:$A$949,"Delhi NCR")</f>
+        <v/>
+      </c>
+      <c r="C49" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A49,'Audit Detail'!$A$4:$A$949,"Bangalore")</f>
+        <v/>
+      </c>
+      <c r="D49" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A49,'Audit Detail'!$A$4:$A$949,"Hyderabad")</f>
+        <v/>
+      </c>
+      <c r="E49" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A49,'Audit Detail'!$A$4:$A$949,"Pune")</f>
+        <v/>
+      </c>
+      <c r="F49" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A49,'Audit Detail'!$A$4:$A$949,"Mumbai")</f>
+        <v/>
+      </c>
+      <c r="G49" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A49,'Audit Detail'!$A$4:$A$949,"Chennai")</f>
+        <v/>
+      </c>
+      <c r="H49" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A49,'Audit Detail'!$A$4:$A$949,"Kolkata")</f>
+        <v/>
+      </c>
+      <c r="I49" s="26">
+        <f>SUM(B49:H49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>Subjective / Fixed</t>
+        </is>
+      </c>
+      <c r="B50" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A50,'Audit Detail'!$A$4:$A$949,"Delhi NCR")</f>
+        <v/>
+      </c>
+      <c r="C50" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A50,'Audit Detail'!$A$4:$A$949,"Bangalore")</f>
+        <v/>
+      </c>
+      <c r="D50" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A50,'Audit Detail'!$A$4:$A$949,"Hyderabad")</f>
+        <v/>
+      </c>
+      <c r="E50" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A50,'Audit Detail'!$A$4:$A$949,"Pune")</f>
+        <v/>
+      </c>
+      <c r="F50" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A50,'Audit Detail'!$A$4:$A$949,"Mumbai")</f>
+        <v/>
+      </c>
+      <c r="G50" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A50,'Audit Detail'!$A$4:$A$949,"Chennai")</f>
+        <v/>
+      </c>
+      <c r="H50" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A50,'Audit Detail'!$A$4:$A$949,"Kolkata")</f>
+        <v/>
+      </c>
+      <c r="I50" s="26">
+        <f>SUM(B50:H50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>Subjective / Evidence Missing</t>
+        </is>
+      </c>
+      <c r="B51" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A51,'Audit Detail'!$A$4:$A$949,"Delhi NCR")</f>
+        <v/>
+      </c>
+      <c r="C51" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A51,'Audit Detail'!$A$4:$A$949,"Bangalore")</f>
+        <v/>
+      </c>
+      <c r="D51" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A51,'Audit Detail'!$A$4:$A$949,"Hyderabad")</f>
+        <v/>
+      </c>
+      <c r="E51" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A51,'Audit Detail'!$A$4:$A$949,"Pune")</f>
+        <v/>
+      </c>
+      <c r="F51" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A51,'Audit Detail'!$A$4:$A$949,"Mumbai")</f>
+        <v/>
+      </c>
+      <c r="G51" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A51,'Audit Detail'!$A$4:$A$949,"Chennai")</f>
+        <v/>
+      </c>
+      <c r="H51" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A51,'Audit Detail'!$A$4:$A$949,"Kolkata")</f>
+        <v/>
+      </c>
+      <c r="I51" s="26">
+        <f>SUM(B51:H51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>Part Formula + Subjective/Incomplete Evidence</t>
+        </is>
+      </c>
+      <c r="B52" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A52,'Audit Detail'!$A$4:$A$949,"Delhi NCR")</f>
+        <v/>
+      </c>
+      <c r="C52" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A52,'Audit Detail'!$A$4:$A$949,"Bangalore")</f>
+        <v/>
+      </c>
+      <c r="D52" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A52,'Audit Detail'!$A$4:$A$949,"Hyderabad")</f>
+        <v/>
+      </c>
+      <c r="E52" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A52,'Audit Detail'!$A$4:$A$949,"Pune")</f>
+        <v/>
+      </c>
+      <c r="F52" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A52,'Audit Detail'!$A$4:$A$949,"Mumbai")</f>
+        <v/>
+      </c>
+      <c r="G52" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A52,'Audit Detail'!$A$4:$A$949,"Chennai")</f>
+        <v/>
+      </c>
+      <c r="H52" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A52,'Audit Detail'!$A$4:$A$949,"Kolkata")</f>
+        <v/>
+      </c>
+      <c r="I52" s="26">
+        <f>SUM(B52:H52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>Subjective</t>
+        </is>
+      </c>
+      <c r="B53" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A53,'Audit Detail'!$A$4:$A$949,"Delhi NCR")</f>
+        <v/>
+      </c>
+      <c r="C53" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A53,'Audit Detail'!$A$4:$A$949,"Bangalore")</f>
+        <v/>
+      </c>
+      <c r="D53" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A53,'Audit Detail'!$A$4:$A$949,"Hyderabad")</f>
+        <v/>
+      </c>
+      <c r="E53" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A53,'Audit Detail'!$A$4:$A$949,"Pune")</f>
+        <v/>
+      </c>
+      <c r="F53" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A53,'Audit Detail'!$A$4:$A$949,"Mumbai")</f>
+        <v/>
+      </c>
+      <c r="G53" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A53,'Audit Detail'!$A$4:$A$949,"Chennai")</f>
+        <v/>
+      </c>
+      <c r="H53" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A53,'Audit Detail'!$A$4:$A$949,"Kolkata")</f>
+        <v/>
+      </c>
+      <c r="I53" s="26">
+        <f>SUM(B53:H53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>Part Formula + Manual/Fixed Component</t>
+        </is>
+      </c>
+      <c r="B54" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A54,'Audit Detail'!$A$4:$A$949,"Delhi NCR")</f>
+        <v/>
+      </c>
+      <c r="C54" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A54,'Audit Detail'!$A$4:$A$949,"Bangalore")</f>
+        <v/>
+      </c>
+      <c r="D54" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A54,'Audit Detail'!$A$4:$A$949,"Hyderabad")</f>
+        <v/>
+      </c>
+      <c r="E54" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A54,'Audit Detail'!$A$4:$A$949,"Pune")</f>
+        <v/>
+      </c>
+      <c r="F54" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A54,'Audit Detail'!$A$4:$A$949,"Mumbai")</f>
+        <v/>
+      </c>
+      <c r="G54" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A54,'Audit Detail'!$A$4:$A$949,"Chennai")</f>
+        <v/>
+      </c>
+      <c r="H54" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A54,'Audit Detail'!$A$4:$A$949,"Kolkata")</f>
+        <v/>
+      </c>
+      <c r="I54" s="26">
+        <f>SUM(B54:H54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>Insufficient Evidence</t>
+        </is>
+      </c>
+      <c r="B55" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A55,'Audit Detail'!$A$4:$A$949,"Delhi NCR")</f>
+        <v/>
+      </c>
+      <c r="C55" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A55,'Audit Detail'!$A$4:$A$949,"Bangalore")</f>
+        <v/>
+      </c>
+      <c r="D55" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A55,'Audit Detail'!$A$4:$A$949,"Hyderabad")</f>
+        <v/>
+      </c>
+      <c r="E55" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A55,'Audit Detail'!$A$4:$A$949,"Pune")</f>
+        <v/>
+      </c>
+      <c r="F55" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A55,'Audit Detail'!$A$4:$A$949,"Mumbai")</f>
+        <v/>
+      </c>
+      <c r="G55" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A55,'Audit Detail'!$A$4:$A$949,"Chennai")</f>
+        <v/>
+      </c>
+      <c r="H55" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A55,'Audit Detail'!$A$4:$A$949,"Kolkata")</f>
+        <v/>
+      </c>
+      <c r="I55" s="26">
+        <f>SUM(B55:H55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B56" s="24">
+        <f>SUM(B49:B55)</f>
+        <v/>
+      </c>
+      <c r="C56" s="24">
+        <f>SUM(C49:C55)</f>
+        <v/>
+      </c>
+      <c r="D56" s="24">
+        <f>SUM(D49:D55)</f>
+        <v/>
+      </c>
+      <c r="E56" s="24">
+        <f>SUM(E49:E55)</f>
+        <v/>
+      </c>
+      <c r="F56" s="24">
+        <f>SUM(F49:F55)</f>
+        <v/>
+      </c>
+      <c r="G56" s="24">
+        <f>SUM(G49:G55)</f>
+        <v/>
+      </c>
+      <c r="H56" s="24">
+        <f>SUM(H49:H55)</f>
+        <v/>
+      </c>
+      <c r="I56" s="24">
+        <f>SUM(I49:I55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>F. CATEGORY × DEPARTMENT  (amount)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>Driver Acquisition</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Driver Operations</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>R&amp;M</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>Vehicle management</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>Supporting Functions</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>Formula Based</t>
+        </is>
+      </c>
+      <c r="B60" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A60,'Audit Detail'!$D$4:$D$949,"Driver Acquisition")</f>
+        <v/>
+      </c>
+      <c r="C60" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A60,'Audit Detail'!$D$4:$D$949,"Driver Operations")</f>
+        <v/>
+      </c>
+      <c r="D60" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A60,'Audit Detail'!$D$4:$D$949,"R&amp;M")</f>
+        <v/>
+      </c>
+      <c r="E60" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A60,'Audit Detail'!$D$4:$D$949,"Vehicle management")</f>
+        <v/>
+      </c>
+      <c r="F60" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A60,'Audit Detail'!$D$4:$D$949,"Supporting Functions")</f>
+        <v/>
+      </c>
+      <c r="G60" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A60,'Audit Detail'!$D$4:$D$949,"Marketing")</f>
+        <v/>
+      </c>
+      <c r="H60" s="26">
+        <f>SUM(B60:G60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>Subjective / Fixed</t>
+        </is>
+      </c>
+      <c r="B61" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A61,'Audit Detail'!$D$4:$D$949,"Driver Acquisition")</f>
+        <v/>
+      </c>
+      <c r="C61" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A61,'Audit Detail'!$D$4:$D$949,"Driver Operations")</f>
+        <v/>
+      </c>
+      <c r="D61" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A61,'Audit Detail'!$D$4:$D$949,"R&amp;M")</f>
+        <v/>
+      </c>
+      <c r="E61" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A61,'Audit Detail'!$D$4:$D$949,"Vehicle management")</f>
+        <v/>
+      </c>
+      <c r="F61" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A61,'Audit Detail'!$D$4:$D$949,"Supporting Functions")</f>
+        <v/>
+      </c>
+      <c r="G61" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A61,'Audit Detail'!$D$4:$D$949,"Marketing")</f>
+        <v/>
+      </c>
+      <c r="H61" s="26">
+        <f>SUM(B61:G61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Subjective / Evidence Missing</t>
+        </is>
+      </c>
+      <c r="B62" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A62,'Audit Detail'!$D$4:$D$949,"Driver Acquisition")</f>
+        <v/>
+      </c>
+      <c r="C62" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A62,'Audit Detail'!$D$4:$D$949,"Driver Operations")</f>
+        <v/>
+      </c>
+      <c r="D62" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A62,'Audit Detail'!$D$4:$D$949,"R&amp;M")</f>
+        <v/>
+      </c>
+      <c r="E62" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A62,'Audit Detail'!$D$4:$D$949,"Vehicle management")</f>
+        <v/>
+      </c>
+      <c r="F62" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A62,'Audit Detail'!$D$4:$D$949,"Supporting Functions")</f>
+        <v/>
+      </c>
+      <c r="G62" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A62,'Audit Detail'!$D$4:$D$949,"Marketing")</f>
+        <v/>
+      </c>
+      <c r="H62" s="26">
+        <f>SUM(B62:G62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>Part Formula + Subjective/Incomplete Evidence</t>
+        </is>
+      </c>
+      <c r="B63" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A63,'Audit Detail'!$D$4:$D$949,"Driver Acquisition")</f>
+        <v/>
+      </c>
+      <c r="C63" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A63,'Audit Detail'!$D$4:$D$949,"Driver Operations")</f>
+        <v/>
+      </c>
+      <c r="D63" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A63,'Audit Detail'!$D$4:$D$949,"R&amp;M")</f>
+        <v/>
+      </c>
+      <c r="E63" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A63,'Audit Detail'!$D$4:$D$949,"Vehicle management")</f>
+        <v/>
+      </c>
+      <c r="F63" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A63,'Audit Detail'!$D$4:$D$949,"Supporting Functions")</f>
+        <v/>
+      </c>
+      <c r="G63" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A63,'Audit Detail'!$D$4:$D$949,"Marketing")</f>
+        <v/>
+      </c>
+      <c r="H63" s="26">
+        <f>SUM(B63:G63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>Subjective</t>
+        </is>
+      </c>
+      <c r="B64" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A64,'Audit Detail'!$D$4:$D$949,"Driver Acquisition")</f>
+        <v/>
+      </c>
+      <c r="C64" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A64,'Audit Detail'!$D$4:$D$949,"Driver Operations")</f>
+        <v/>
+      </c>
+      <c r="D64" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A64,'Audit Detail'!$D$4:$D$949,"R&amp;M")</f>
+        <v/>
+      </c>
+      <c r="E64" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A64,'Audit Detail'!$D$4:$D$949,"Vehicle management")</f>
+        <v/>
+      </c>
+      <c r="F64" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A64,'Audit Detail'!$D$4:$D$949,"Supporting Functions")</f>
+        <v/>
+      </c>
+      <c r="G64" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A64,'Audit Detail'!$D$4:$D$949,"Marketing")</f>
+        <v/>
+      </c>
+      <c r="H64" s="26">
+        <f>SUM(B64:G64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>Part Formula + Manual/Fixed Component</t>
+        </is>
+      </c>
+      <c r="B65" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A65,'Audit Detail'!$D$4:$D$949,"Driver Acquisition")</f>
+        <v/>
+      </c>
+      <c r="C65" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A65,'Audit Detail'!$D$4:$D$949,"Driver Operations")</f>
+        <v/>
+      </c>
+      <c r="D65" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A65,'Audit Detail'!$D$4:$D$949,"R&amp;M")</f>
+        <v/>
+      </c>
+      <c r="E65" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A65,'Audit Detail'!$D$4:$D$949,"Vehicle management")</f>
+        <v/>
+      </c>
+      <c r="F65" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A65,'Audit Detail'!$D$4:$D$949,"Supporting Functions")</f>
+        <v/>
+      </c>
+      <c r="G65" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A65,'Audit Detail'!$D$4:$D$949,"Marketing")</f>
+        <v/>
+      </c>
+      <c r="H65" s="26">
+        <f>SUM(B65:G65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>Insufficient Evidence</t>
+        </is>
+      </c>
+      <c r="B66" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A66,'Audit Detail'!$D$4:$D$949,"Driver Acquisition")</f>
+        <v/>
+      </c>
+      <c r="C66" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A66,'Audit Detail'!$D$4:$D$949,"Driver Operations")</f>
+        <v/>
+      </c>
+      <c r="D66" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A66,'Audit Detail'!$D$4:$D$949,"R&amp;M")</f>
+        <v/>
+      </c>
+      <c r="E66" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A66,'Audit Detail'!$D$4:$D$949,"Vehicle management")</f>
+        <v/>
+      </c>
+      <c r="F66" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A66,'Audit Detail'!$D$4:$D$949,"Supporting Functions")</f>
+        <v/>
+      </c>
+      <c r="G66" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$G$4:$G$949,$A66,'Audit Detail'!$D$4:$D$949,"Marketing")</f>
+        <v/>
+      </c>
+      <c r="H66" s="26">
+        <f>SUM(B66:G66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B67" s="24">
+        <f>SUM(B60:B66)</f>
+        <v/>
+      </c>
+      <c r="C67" s="24">
+        <f>SUM(C60:C66)</f>
+        <v/>
+      </c>
+      <c r="D67" s="24">
+        <f>SUM(D60:D66)</f>
+        <v/>
+      </c>
+      <c r="E67" s="24">
+        <f>SUM(E60:E66)</f>
+        <v/>
+      </c>
+      <c r="F67" s="24">
+        <f>SUM(F60:F66)</f>
+        <v/>
+      </c>
+      <c r="G67" s="24">
+        <f>SUM(G60:G66)</f>
+        <v/>
+      </c>
+      <c r="H67" s="24">
+        <f>SUM(H60:H66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>G. DEPARTMENT × CATEGORY  (amount) — full pivot, all departments × all categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>Formula Based</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Subjective / Fixed</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>Subjective / Evidence Missing</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>Part Formula + Subjective/Incomplete Evidence</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>Subjective</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>Part Formula + Manual/Fixed Component</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>Insufficient Evidence</t>
+        </is>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+      <c r="B71" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A71,'Audit Detail'!$G$4:$G$949,"Formula Based")</f>
+        <v/>
+      </c>
+      <c r="C71" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A71,'Audit Detail'!$G$4:$G$949,"Subjective / Fixed")</f>
+        <v/>
+      </c>
+      <c r="D71" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A71,'Audit Detail'!$G$4:$G$949,"Subjective / Evidence Missing")</f>
+        <v/>
+      </c>
+      <c r="E71" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A71,'Audit Detail'!$G$4:$G$949,"Part Formula + Subjective/Incomplete Evidence")</f>
+        <v/>
+      </c>
+      <c r="F71" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A71,'Audit Detail'!$G$4:$G$949,"Subjective")</f>
+        <v/>
+      </c>
+      <c r="G71" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A71,'Audit Detail'!$G$4:$G$949,"Part Formula + Manual/Fixed Component")</f>
+        <v/>
+      </c>
+      <c r="H71" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A71,'Audit Detail'!$G$4:$G$949,"Insufficient Evidence")</f>
+        <v/>
+      </c>
+      <c r="I71" s="26">
+        <f>SUM(B71:H71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>Driver Acquisition</t>
+        </is>
+      </c>
+      <c r="B72" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A72,'Audit Detail'!$G$4:$G$949,"Formula Based")</f>
+        <v/>
+      </c>
+      <c r="C72" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A72,'Audit Detail'!$G$4:$G$949,"Subjective / Fixed")</f>
+        <v/>
+      </c>
+      <c r="D72" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A72,'Audit Detail'!$G$4:$G$949,"Subjective / Evidence Missing")</f>
+        <v/>
+      </c>
+      <c r="E72" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A72,'Audit Detail'!$G$4:$G$949,"Part Formula + Subjective/Incomplete Evidence")</f>
+        <v/>
+      </c>
+      <c r="F72" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A72,'Audit Detail'!$G$4:$G$949,"Subjective")</f>
+        <v/>
+      </c>
+      <c r="G72" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A72,'Audit Detail'!$G$4:$G$949,"Part Formula + Manual/Fixed Component")</f>
+        <v/>
+      </c>
+      <c r="H72" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A72,'Audit Detail'!$G$4:$G$949,"Insufficient Evidence")</f>
+        <v/>
+      </c>
+      <c r="I72" s="26">
+        <f>SUM(B72:H72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>Driver Operations</t>
+        </is>
+      </c>
+      <c r="B73" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A73,'Audit Detail'!$G$4:$G$949,"Formula Based")</f>
+        <v/>
+      </c>
+      <c r="C73" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A73,'Audit Detail'!$G$4:$G$949,"Subjective / Fixed")</f>
+        <v/>
+      </c>
+      <c r="D73" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A73,'Audit Detail'!$G$4:$G$949,"Subjective / Evidence Missing")</f>
+        <v/>
+      </c>
+      <c r="E73" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A73,'Audit Detail'!$G$4:$G$949,"Part Formula + Subjective/Incomplete Evidence")</f>
+        <v/>
+      </c>
+      <c r="F73" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A73,'Audit Detail'!$G$4:$G$949,"Subjective")</f>
+        <v/>
+      </c>
+      <c r="G73" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A73,'Audit Detail'!$G$4:$G$949,"Part Formula + Manual/Fixed Component")</f>
+        <v/>
+      </c>
+      <c r="H73" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A73,'Audit Detail'!$G$4:$G$949,"Insufficient Evidence")</f>
+        <v/>
+      </c>
+      <c r="I73" s="26">
+        <f>SUM(B73:H73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B74" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A74,'Audit Detail'!$G$4:$G$949,"Formula Based")</f>
+        <v/>
+      </c>
+      <c r="C74" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A74,'Audit Detail'!$G$4:$G$949,"Subjective / Fixed")</f>
+        <v/>
+      </c>
+      <c r="D74" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A74,'Audit Detail'!$G$4:$G$949,"Subjective / Evidence Missing")</f>
+        <v/>
+      </c>
+      <c r="E74" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A74,'Audit Detail'!$G$4:$G$949,"Part Formula + Subjective/Incomplete Evidence")</f>
+        <v/>
+      </c>
+      <c r="F74" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A74,'Audit Detail'!$G$4:$G$949,"Subjective")</f>
+        <v/>
+      </c>
+      <c r="G74" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A74,'Audit Detail'!$G$4:$G$949,"Part Formula + Manual/Fixed Component")</f>
+        <v/>
+      </c>
+      <c r="H74" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A74,'Audit Detail'!$G$4:$G$949,"Insufficient Evidence")</f>
+        <v/>
+      </c>
+      <c r="I74" s="26">
+        <f>SUM(B74:H74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>R&amp;M</t>
+        </is>
+      </c>
+      <c r="B75" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A75,'Audit Detail'!$G$4:$G$949,"Formula Based")</f>
+        <v/>
+      </c>
+      <c r="C75" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A75,'Audit Detail'!$G$4:$G$949,"Subjective / Fixed")</f>
+        <v/>
+      </c>
+      <c r="D75" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A75,'Audit Detail'!$G$4:$G$949,"Subjective / Evidence Missing")</f>
+        <v/>
+      </c>
+      <c r="E75" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A75,'Audit Detail'!$G$4:$G$949,"Part Formula + Subjective/Incomplete Evidence")</f>
+        <v/>
+      </c>
+      <c r="F75" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A75,'Audit Detail'!$G$4:$G$949,"Subjective")</f>
+        <v/>
+      </c>
+      <c r="G75" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A75,'Audit Detail'!$G$4:$G$949,"Part Formula + Manual/Fixed Component")</f>
+        <v/>
+      </c>
+      <c r="H75" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A75,'Audit Detail'!$G$4:$G$949,"Insufficient Evidence")</f>
+        <v/>
+      </c>
+      <c r="I75" s="26">
+        <f>SUM(B75:H75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>Supporting Functions</t>
+        </is>
+      </c>
+      <c r="B76" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A76,'Audit Detail'!$G$4:$G$949,"Formula Based")</f>
+        <v/>
+      </c>
+      <c r="C76" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A76,'Audit Detail'!$G$4:$G$949,"Subjective / Fixed")</f>
+        <v/>
+      </c>
+      <c r="D76" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A76,'Audit Detail'!$G$4:$G$949,"Subjective / Evidence Missing")</f>
+        <v/>
+      </c>
+      <c r="E76" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A76,'Audit Detail'!$G$4:$G$949,"Part Formula + Subjective/Incomplete Evidence")</f>
+        <v/>
+      </c>
+      <c r="F76" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A76,'Audit Detail'!$G$4:$G$949,"Subjective")</f>
+        <v/>
+      </c>
+      <c r="G76" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A76,'Audit Detail'!$G$4:$G$949,"Part Formula + Manual/Fixed Component")</f>
+        <v/>
+      </c>
+      <c r="H76" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A76,'Audit Detail'!$G$4:$G$949,"Insufficient Evidence")</f>
+        <v/>
+      </c>
+      <c r="I76" s="26">
+        <f>SUM(B76:H76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B77" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A77,'Audit Detail'!$G$4:$G$949,"Formula Based")</f>
+        <v/>
+      </c>
+      <c r="C77" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A77,'Audit Detail'!$G$4:$G$949,"Subjective / Fixed")</f>
+        <v/>
+      </c>
+      <c r="D77" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A77,'Audit Detail'!$G$4:$G$949,"Subjective / Evidence Missing")</f>
+        <v/>
+      </c>
+      <c r="E77" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A77,'Audit Detail'!$G$4:$G$949,"Part Formula + Subjective/Incomplete Evidence")</f>
+        <v/>
+      </c>
+      <c r="F77" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A77,'Audit Detail'!$G$4:$G$949,"Subjective")</f>
+        <v/>
+      </c>
+      <c r="G77" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A77,'Audit Detail'!$G$4:$G$949,"Part Formula + Manual/Fixed Component")</f>
+        <v/>
+      </c>
+      <c r="H77" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A77,'Audit Detail'!$G$4:$G$949,"Insufficient Evidence")</f>
+        <v/>
+      </c>
+      <c r="I77" s="26">
+        <f>SUM(B77:H77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>Vehicle management</t>
+        </is>
+      </c>
+      <c r="B78" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A78,'Audit Detail'!$G$4:$G$949,"Formula Based")</f>
+        <v/>
+      </c>
+      <c r="C78" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A78,'Audit Detail'!$G$4:$G$949,"Subjective / Fixed")</f>
+        <v/>
+      </c>
+      <c r="D78" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A78,'Audit Detail'!$G$4:$G$949,"Subjective / Evidence Missing")</f>
+        <v/>
+      </c>
+      <c r="E78" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A78,'Audit Detail'!$G$4:$G$949,"Part Formula + Subjective/Incomplete Evidence")</f>
+        <v/>
+      </c>
+      <c r="F78" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A78,'Audit Detail'!$G$4:$G$949,"Subjective")</f>
+        <v/>
+      </c>
+      <c r="G78" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A78,'Audit Detail'!$G$4:$G$949,"Part Formula + Manual/Fixed Component")</f>
+        <v/>
+      </c>
+      <c r="H78" s="11">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$D$4:$D$949,$A78,'Audit Detail'!$G$4:$G$949,"Insufficient Evidence")</f>
+        <v/>
+      </c>
+      <c r="I78" s="26">
+        <f>SUM(B78:H78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="22" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
+        </is>
+      </c>
+      <c r="B79" s="24">
+        <f>SUM(B71:B78)</f>
+        <v/>
+      </c>
+      <c r="C79" s="24">
+        <f>SUM(C71:C78)</f>
+        <v/>
+      </c>
+      <c r="D79" s="24">
+        <f>SUM(D71:D78)</f>
+        <v/>
+      </c>
+      <c r="E79" s="24">
+        <f>SUM(E71:E78)</f>
+        <v/>
+      </c>
+      <c r="F79" s="24">
+        <f>SUM(F71:F78)</f>
+        <v/>
+      </c>
+      <c r="G79" s="24">
+        <f>SUM(G71:G78)</f>
+        <v/>
+      </c>
+      <c r="H79" s="24">
+        <f>SUM(H71:H78)</f>
+        <v/>
+      </c>
+      <c r="I79" s="24">
+        <f>SUM(I71:I78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>H. BY FINAL STATUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>Final Status</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>Employees</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>Total Amount</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>Avg per Employee</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>% of Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="B83" s="19">
+        <f>COUNTIF('Audit Detail'!$H$4:$H$949,$A83)</f>
+        <v/>
+      </c>
+      <c r="C83" s="20">
+        <f>SUMIF('Audit Detail'!$H$4:$H$949,$A83,'Audit Detail'!$J$4:$J$949)</f>
+        <v/>
+      </c>
+      <c r="D83" s="20">
+        <f>IF(B83=0,0,C83/B83)</f>
+        <v/>
+      </c>
+      <c r="E83" s="21">
+        <f>IF($C$90=0,"",C83/$C$90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="19" t="inlineStr">
+        <is>
+          <t>Insufficient Evidence</t>
+        </is>
+      </c>
+      <c r="B84" s="19">
+        <f>COUNTIF('Audit Detail'!$H$4:$H$949,$A84)</f>
+        <v/>
+      </c>
+      <c r="C84" s="20">
+        <f>SUMIF('Audit Detail'!$H$4:$H$949,$A84,'Audit Detail'!$J$4:$J$949)</f>
+        <v/>
+      </c>
+      <c r="D84" s="20">
+        <f>IF(B84=0,0,C84/B84)</f>
+        <v/>
+      </c>
+      <c r="E84" s="21">
+        <f>IF($C$90=0,"",C84/$C$90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="19" t="inlineStr">
+        <is>
+          <t>Mismatch — Overpaid</t>
+        </is>
+      </c>
+      <c r="B85" s="19">
+        <f>COUNTIF('Audit Detail'!$H$4:$H$949,$A85)</f>
+        <v/>
+      </c>
+      <c r="C85" s="20">
+        <f>SUMIF('Audit Detail'!$H$4:$H$949,$A85,'Audit Detail'!$J$4:$J$949)</f>
+        <v/>
+      </c>
+      <c r="D85" s="20">
+        <f>IF(B85=0,0,C85/B85)</f>
+        <v/>
+      </c>
+      <c r="E85" s="21">
+        <f>IF($C$90=0,"",C85/$C$90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="19" t="inlineStr">
+        <is>
+          <t>Mismatch — Underpaid</t>
+        </is>
+      </c>
+      <c r="B86" s="19">
+        <f>COUNTIF('Audit Detail'!$H$4:$H$949,$A86)</f>
+        <v/>
+      </c>
+      <c r="C86" s="20">
+        <f>SUMIF('Audit Detail'!$H$4:$H$949,$A86,'Audit Detail'!$J$4:$J$949)</f>
+        <v/>
+      </c>
+      <c r="D86" s="20">
+        <f>IF(B86=0,0,C86/B86)</f>
+        <v/>
+      </c>
+      <c r="E86" s="21">
+        <f>IF($C$90=0,"",C86/$C$90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="19" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
+      </c>
+      <c r="B87" s="19">
+        <f>COUNTIF('Audit Detail'!$H$4:$H$949,$A87)</f>
+        <v/>
+      </c>
+      <c r="C87" s="20">
+        <f>SUMIF('Audit Detail'!$H$4:$H$949,$A87,'Audit Detail'!$J$4:$J$949)</f>
+        <v/>
+      </c>
+      <c r="D87" s="20">
+        <f>IF(B87=0,0,C87/B87)</f>
+        <v/>
+      </c>
+      <c r="E87" s="21">
+        <f>IF($C$90=0,"",C87/$C$90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="19" t="inlineStr">
+        <is>
+          <t>Insufficient Evidence — No Overpayment</t>
+        </is>
+      </c>
+      <c r="B88" s="19">
+        <f>COUNTIF('Audit Detail'!$H$4:$H$949,$A88)</f>
+        <v/>
+      </c>
+      <c r="C88" s="20">
+        <f>SUMIF('Audit Detail'!$H$4:$H$949,$A88,'Audit Detail'!$J$4:$J$949)</f>
+        <v/>
+      </c>
+      <c r="D88" s="20">
+        <f>IF(B88=0,0,C88/B88)</f>
+        <v/>
+      </c>
+      <c r="E88" s="21">
+        <f>IF($C$90=0,"",C88/$C$90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="19" t="inlineStr">
+        <is>
+          <t>Mismatch — Overpaid / Evidence Incomplete</t>
+        </is>
+      </c>
+      <c r="B89" s="19">
+        <f>COUNTIF('Audit Detail'!$H$4:$H$949,$A89)</f>
+        <v/>
+      </c>
+      <c r="C89" s="20">
+        <f>SUMIF('Audit Detail'!$H$4:$H$949,$A89,'Audit Detail'!$J$4:$J$949)</f>
+        <v/>
+      </c>
+      <c r="D89" s="20">
+        <f>IF(B89=0,0,C89/B89)</f>
+        <v/>
+      </c>
+      <c r="E89" s="21">
+        <f>IF($C$90=0,"",C89/$C$90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B90" s="23">
+        <f>SUM(B83:B89)</f>
+        <v/>
+      </c>
+      <c r="C90" s="24">
+        <f>SUM(C83:C89)</f>
+        <v/>
+      </c>
+      <c r="D90" s="27">
+        <f>IF(B90=0,0,C90/B90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>I. BY RISK LEVEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
           <t>Risk Level</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B93" s="9" t="inlineStr">
         <is>
           <t>Employees</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C93" s="9" t="inlineStr">
         <is>
           <t>Total Amount</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D93" s="9" t="inlineStr">
         <is>
           <t>Avg per Employee</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E93" s="9" t="inlineStr">
         <is>
           <t>% of Total</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="19" t="inlineStr">
         <is>
           <t>No Risk</t>
         </is>
       </c>
-      <c r="B27" s="19">
-        <f>COUNTIF('Audit Detail'!$I$4:$I$949,$A27)</f>
-        <v/>
-      </c>
-      <c r="C27" s="20">
-        <f>SUMIF('Audit Detail'!$I$4:$I$949,$A27,'Audit Detail'!$J$4:$J$949)</f>
-        <v/>
-      </c>
-      <c r="D27" s="20">
-        <f>IF(B27=0,0,C27/B27)</f>
-        <v/>
-      </c>
-      <c r="E27" s="21">
-        <f>IF($C$31=0,"",C27/$C$31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="B94" s="19">
+        <f>COUNTIF('Audit Detail'!$I$4:$I$949,$A94)</f>
+        <v/>
+      </c>
+      <c r="C94" s="20">
+        <f>SUMIF('Audit Detail'!$I$4:$I$949,$A94,'Audit Detail'!$J$4:$J$949)</f>
+        <v/>
+      </c>
+      <c r="D94" s="20">
+        <f>IF(B94=0,0,C94/B94)</f>
+        <v/>
+      </c>
+      <c r="E94" s="21">
+        <f>IF($C$98=0,"",C94/$C$98)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B28" s="19">
-        <f>COUNTIF('Audit Detail'!$I$4:$I$949,$A28)</f>
-        <v/>
-      </c>
-      <c r="C28" s="20">
-        <f>SUMIF('Audit Detail'!$I$4:$I$949,$A28,'Audit Detail'!$J$4:$J$949)</f>
-        <v/>
-      </c>
-      <c r="D28" s="20">
-        <f>IF(B28=0,0,C28/B28)</f>
-        <v/>
-      </c>
-      <c r="E28" s="21">
-        <f>IF($C$31=0,"",C28/$C$31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="B95" s="19">
+        <f>COUNTIF('Audit Detail'!$I$4:$I$949,$A95)</f>
+        <v/>
+      </c>
+      <c r="C95" s="20">
+        <f>SUMIF('Audit Detail'!$I$4:$I$949,$A95,'Audit Detail'!$J$4:$J$949)</f>
+        <v/>
+      </c>
+      <c r="D95" s="20">
+        <f>IF(B95=0,0,C95/B95)</f>
+        <v/>
+      </c>
+      <c r="E95" s="21">
+        <f>IF($C$98=0,"",C95/$C$98)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="19" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B29" s="19">
-        <f>COUNTIF('Audit Detail'!$I$4:$I$949,$A29)</f>
-        <v/>
-      </c>
-      <c r="C29" s="20">
-        <f>SUMIF('Audit Detail'!$I$4:$I$949,$A29,'Audit Detail'!$J$4:$J$949)</f>
-        <v/>
-      </c>
-      <c r="D29" s="20">
-        <f>IF(B29=0,0,C29/B29)</f>
-        <v/>
-      </c>
-      <c r="E29" s="21">
-        <f>IF($C$31=0,"",C29/$C$31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="B96" s="19">
+        <f>COUNTIF('Audit Detail'!$I$4:$I$949,$A96)</f>
+        <v/>
+      </c>
+      <c r="C96" s="20">
+        <f>SUMIF('Audit Detail'!$I$4:$I$949,$A96,'Audit Detail'!$J$4:$J$949)</f>
+        <v/>
+      </c>
+      <c r="D96" s="20">
+        <f>IF(B96=0,0,C96/B96)</f>
+        <v/>
+      </c>
+      <c r="E96" s="21">
+        <f>IF($C$98=0,"",C96/$C$98)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="19" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B30" s="19">
-        <f>COUNTIF('Audit Detail'!$I$4:$I$949,$A30)</f>
-        <v/>
-      </c>
-      <c r="C30" s="20">
-        <f>SUMIF('Audit Detail'!$I$4:$I$949,$A30,'Audit Detail'!$J$4:$J$949)</f>
-        <v/>
-      </c>
-      <c r="D30" s="20">
-        <f>IF(B30=0,0,C30/B30)</f>
-        <v/>
-      </c>
-      <c r="E30" s="21">
-        <f>IF($C$31=0,"",C30/$C$31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="B97" s="19">
+        <f>COUNTIF('Audit Detail'!$I$4:$I$949,$A97)</f>
+        <v/>
+      </c>
+      <c r="C97" s="20">
+        <f>SUMIF('Audit Detail'!$I$4:$I$949,$A97,'Audit Detail'!$J$4:$J$949)</f>
+        <v/>
+      </c>
+      <c r="D97" s="20">
+        <f>IF(B97=0,0,C97/B97)</f>
+        <v/>
+      </c>
+      <c r="E97" s="21">
+        <f>IF($C$98=0,"",C97/$C$98)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="22" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B31" s="23">
-        <f>SUM(B27:B30)</f>
-        <v/>
-      </c>
-      <c r="C31" s="24">
-        <f>SUM(C27:C30)</f>
-        <v/>
-      </c>
-      <c r="D31" s="25">
-        <f>IF(B31=0,0,C31/B31)</f>
+      <c r="B98" s="23">
+        <f>SUM(B94:B97)</f>
+        <v/>
+      </c>
+      <c r="C98" s="24">
+        <f>SUM(C94:C97)</f>
+        <v/>
+      </c>
+      <c r="D98" s="27">
+        <f>IF(B98=0,0,C98/B98)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="11">
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A92:H92"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A81:H81"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="A58:H58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -13373,7 +15982,7 @@
         <f>SUM(G5:G11)</f>
         <v/>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="28">
         <f>IF(B12=0,"",F12/B12)</f>
         <v/>
       </c>
@@ -13417,12 +16026,12 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
           <t>Supporting Functions</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>Marketing</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -13454,11 +16063,11 @@
         <v/>
       </c>
       <c r="F16" s="20">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A16,'Audit Detail'!$D$4:$D$949,"(blank)")</f>
+        <v/>
+      </c>
+      <c r="G16" s="20">
         <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A16,'Audit Detail'!$D$4:$D$949,"Supporting Functions")</f>
-        <v/>
-      </c>
-      <c r="G16" s="20">
-        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A16,'Audit Detail'!$D$4:$D$949,"Marketing")</f>
         <v/>
       </c>
       <c r="H16" s="20">
@@ -13489,11 +16098,11 @@
         <v/>
       </c>
       <c r="F17" s="20">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A17,'Audit Detail'!$D$4:$D$949,"(blank)")</f>
+        <v/>
+      </c>
+      <c r="G17" s="20">
         <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A17,'Audit Detail'!$D$4:$D$949,"Supporting Functions")</f>
-        <v/>
-      </c>
-      <c r="G17" s="20">
-        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A17,'Audit Detail'!$D$4:$D$949,"Marketing")</f>
         <v/>
       </c>
       <c r="H17" s="20">
@@ -13524,11 +16133,11 @@
         <v/>
       </c>
       <c r="F18" s="20">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A18,'Audit Detail'!$D$4:$D$949,"(blank)")</f>
+        <v/>
+      </c>
+      <c r="G18" s="20">
         <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A18,'Audit Detail'!$D$4:$D$949,"Supporting Functions")</f>
-        <v/>
-      </c>
-      <c r="G18" s="20">
-        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A18,'Audit Detail'!$D$4:$D$949,"Marketing")</f>
         <v/>
       </c>
       <c r="H18" s="20">
@@ -13559,11 +16168,11 @@
         <v/>
       </c>
       <c r="F19" s="20">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A19,'Audit Detail'!$D$4:$D$949,"(blank)")</f>
+        <v/>
+      </c>
+      <c r="G19" s="20">
         <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A19,'Audit Detail'!$D$4:$D$949,"Supporting Functions")</f>
-        <v/>
-      </c>
-      <c r="G19" s="20">
-        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A19,'Audit Detail'!$D$4:$D$949,"Marketing")</f>
         <v/>
       </c>
       <c r="H19" s="20">
@@ -13594,11 +16203,11 @@
         <v/>
       </c>
       <c r="F20" s="20">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A20,'Audit Detail'!$D$4:$D$949,"(blank)")</f>
+        <v/>
+      </c>
+      <c r="G20" s="20">
         <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A20,'Audit Detail'!$D$4:$D$949,"Supporting Functions")</f>
-        <v/>
-      </c>
-      <c r="G20" s="20">
-        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A20,'Audit Detail'!$D$4:$D$949,"Marketing")</f>
         <v/>
       </c>
       <c r="H20" s="20">
@@ -13629,11 +16238,11 @@
         <v/>
       </c>
       <c r="F21" s="20">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A21,'Audit Detail'!$D$4:$D$949,"(blank)")</f>
+        <v/>
+      </c>
+      <c r="G21" s="20">
         <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A21,'Audit Detail'!$D$4:$D$949,"Supporting Functions")</f>
-        <v/>
-      </c>
-      <c r="G21" s="20">
-        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A21,'Audit Detail'!$D$4:$D$949,"Marketing")</f>
         <v/>
       </c>
       <c r="H21" s="20">
@@ -13664,11 +16273,11 @@
         <v/>
       </c>
       <c r="F22" s="20">
+        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A22,'Audit Detail'!$D$4:$D$949,"(blank)")</f>
+        <v/>
+      </c>
+      <c r="G22" s="20">
         <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A22,'Audit Detail'!$D$4:$D$949,"Supporting Functions")</f>
-        <v/>
-      </c>
-      <c r="G22" s="20">
-        <f>SUMIFS('Audit Detail'!$J$4:$J$949,'Audit Detail'!$A$4:$A$949,$A22,'Audit Detail'!$D$4:$D$949,"Marketing")</f>
         <v/>
       </c>
       <c r="H22" s="20">
@@ -18045,7 +20654,7 @@
         <f>SUM(E5:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="29">
         <f>IF(C12=0,"",E12/C12)</f>
         <v/>
       </c>
@@ -18235,61 +20844,61 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="28" t="inlineStr">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>Final amount — all rows</t>
         </is>
       </c>
-      <c r="B26" s="29" t="n"/>
-      <c r="C26" s="30">
+      <c r="B26" s="31" t="n"/>
+      <c r="C26" s="32">
         <f>'Audit Detail'!J950</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="28" t="inlineStr">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>BI amount — all rows</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n"/>
-      <c r="C27" s="30">
+      <c r="B27" s="31" t="n"/>
+      <c r="C27" s="32">
         <f>'Audit Detail'!K950</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="28" t="inlineStr">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>Risk amount as reported (BI − Final, all rows)</t>
         </is>
       </c>
-      <c r="B28" s="29" t="n"/>
-      <c r="C28" s="30">
+      <c r="B28" s="31" t="n"/>
+      <c r="C28" s="32">
         <f>'Audit Detail'!L950</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="31" t="inlineStr">
+      <c r="A29" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  of which: rows where BI was computed</t>
         </is>
       </c>
-      <c r="B29" s="29" t="n"/>
-      <c r="C29" s="30">
+      <c r="B29" s="31" t="n"/>
+      <c r="C29" s="32">
         <f>E12</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="31" t="inlineStr">
+      <c r="A30" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  of which: rows with no BI value (gap, not overpayment)</t>
         </is>
       </c>
-      <c r="B30" s="29" t="n"/>
-      <c r="C30" s="30">
+      <c r="B30" s="31" t="n"/>
+      <c r="C30" s="32">
         <f>-C23</f>
         <v/>
       </c>
@@ -18434,7 +21043,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A4,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="34">
         <f>SUM(B4:E4)</f>
         <v/>
       </c>
@@ -18454,7 +21063,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A4,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K4" s="32">
+      <c r="K4" s="34">
         <f>SUM(G4:J4)</f>
         <v/>
       </c>
@@ -18489,7 +21098,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A5,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="34">
         <f>SUM(B5:E5)</f>
         <v/>
       </c>
@@ -18509,7 +21118,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A5,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K5" s="32">
+      <c r="K5" s="34">
         <f>SUM(G5:J5)</f>
         <v/>
       </c>
@@ -18544,7 +21153,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A6,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="34">
         <f>SUM(B6:E6)</f>
         <v/>
       </c>
@@ -18564,7 +21173,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A6,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K6" s="32">
+      <c r="K6" s="34">
         <f>SUM(G6:J6)</f>
         <v/>
       </c>
@@ -18599,7 +21208,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A7,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="34">
         <f>SUM(B7:E7)</f>
         <v/>
       </c>
@@ -18619,7 +21228,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A7,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K7" s="32">
+      <c r="K7" s="34">
         <f>SUM(G7:J7)</f>
         <v/>
       </c>
@@ -18654,7 +21263,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A8,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="34">
         <f>SUM(B8:E8)</f>
         <v/>
       </c>
@@ -18674,7 +21283,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A8,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K8" s="32">
+      <c r="K8" s="34">
         <f>SUM(G8:J8)</f>
         <v/>
       </c>
@@ -18709,7 +21318,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A9,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="34">
         <f>SUM(B9:E9)</f>
         <v/>
       </c>
@@ -18729,7 +21338,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A9,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K9" s="32">
+      <c r="K9" s="34">
         <f>SUM(G9:J9)</f>
         <v/>
       </c>
@@ -18764,7 +21373,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A10,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="34">
         <f>SUM(B10:E10)</f>
         <v/>
       </c>
@@ -18784,7 +21393,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A10,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K10" s="32">
+      <c r="K10" s="34">
         <f>SUM(G10:J10)</f>
         <v/>
       </c>
@@ -18819,7 +21428,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A11,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="34">
         <f>SUM(B11:E11)</f>
         <v/>
       </c>
@@ -18839,7 +21448,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A11,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K11" s="32">
+      <c r="K11" s="34">
         <f>SUM(G11:J11)</f>
         <v/>
       </c>
@@ -18874,7 +21483,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A12,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="34">
         <f>SUM(B12:E12)</f>
         <v/>
       </c>
@@ -18894,7 +21503,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A12,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K12" s="32">
+      <c r="K12" s="34">
         <f>SUM(G12:J12)</f>
         <v/>
       </c>
@@ -18929,7 +21538,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A13,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="34">
         <f>SUM(B13:E13)</f>
         <v/>
       </c>
@@ -18949,7 +21558,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A13,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K13" s="32">
+      <c r="K13" s="34">
         <f>SUM(G13:J13)</f>
         <v/>
       </c>
@@ -18984,7 +21593,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A14,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="34">
         <f>SUM(B14:E14)</f>
         <v/>
       </c>
@@ -19004,7 +21613,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A14,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K14" s="32">
+      <c r="K14" s="34">
         <f>SUM(G14:J14)</f>
         <v/>
       </c>
@@ -19039,7 +21648,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A15,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F15" s="32">
+      <c r="F15" s="34">
         <f>SUM(B15:E15)</f>
         <v/>
       </c>
@@ -19059,7 +21668,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$A$4:$A$313,$A15,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K15" s="32">
+      <c r="K15" s="34">
         <f>SUM(G15:J15)</f>
         <v/>
       </c>
@@ -19122,7 +21731,7 @@
         <f>SUM(L4:L15)</f>
         <v/>
       </c>
-      <c r="M16" s="27">
+      <c r="M16" s="29">
         <f>IF(F16=0,"",K16/F16-1)</f>
         <v/>
       </c>
@@ -19264,7 +21873,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$B$4:$B$313,$A4,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="34">
         <f>SUM(B4:E4)</f>
         <v/>
       </c>
@@ -19284,7 +21893,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$B$4:$B$313,$A4,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K4" s="32">
+      <c r="K4" s="34">
         <f>SUM(G4:J4)</f>
         <v/>
       </c>
@@ -19319,7 +21928,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$B$4:$B$313,$A5,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="34">
         <f>SUM(B5:E5)</f>
         <v/>
       </c>
@@ -19339,7 +21948,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$B$4:$B$313,$A5,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K5" s="32">
+      <c r="K5" s="34">
         <f>SUM(G5:J5)</f>
         <v/>
       </c>
@@ -19374,7 +21983,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$B$4:$B$313,$A6,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="34">
         <f>SUM(B6:E6)</f>
         <v/>
       </c>
@@ -19394,7 +22003,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$B$4:$B$313,$A6,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K6" s="32">
+      <c r="K6" s="34">
         <f>SUM(G6:J6)</f>
         <v/>
       </c>
@@ -19429,7 +22038,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$B$4:$B$313,$A7,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="34">
         <f>SUM(B7:E7)</f>
         <v/>
       </c>
@@ -19449,7 +22058,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$B$4:$B$313,$A7,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K7" s="32">
+      <c r="K7" s="34">
         <f>SUM(G7:J7)</f>
         <v/>
       </c>
@@ -19484,7 +22093,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$B$4:$B$313,$A8,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="34">
         <f>SUM(B8:E8)</f>
         <v/>
       </c>
@@ -19504,7 +22113,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$B$4:$B$313,$A8,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K8" s="32">
+      <c r="K8" s="34">
         <f>SUM(G8:J8)</f>
         <v/>
       </c>
@@ -19539,7 +22148,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$B$4:$B$313,$A9,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="34">
         <f>SUM(B9:E9)</f>
         <v/>
       </c>
@@ -19559,7 +22168,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$B$4:$B$313,$A9,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K9" s="32">
+      <c r="K9" s="34">
         <f>SUM(G9:J9)</f>
         <v/>
       </c>
@@ -19594,7 +22203,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$B$4:$B$313,$A10,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="34">
         <f>SUM(B10:E10)</f>
         <v/>
       </c>
@@ -19614,7 +22223,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$B$4:$B$313,$A10,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K10" s="32">
+      <c r="K10" s="34">
         <f>SUM(G10:J10)</f>
         <v/>
       </c>
@@ -19649,7 +22258,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$B$4:$B$313,$A11,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2025)</f>
         <v/>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="34">
         <f>SUM(B11:E11)</f>
         <v/>
       </c>
@@ -19669,7 +22278,7 @@
         <f>SUMIFS('MOM Data'!$E$4:$E$313,'MOM Data'!$B$4:$B$313,$A11,'MOM Data'!$C$4:$C$313,"July",'MOM Data'!$D$4:$D$313,2026)</f>
         <v/>
       </c>
-      <c r="K11" s="32">
+      <c r="K11" s="34">
         <f>SUM(G11:J11)</f>
         <v/>
       </c>
@@ -19732,7 +22341,7 @@
         <f>SUM(L4:L11)</f>
         <v/>
       </c>
-      <c r="M12" s="27">
+      <c r="M12" s="29">
         <f>IF(F12=0,"",K12/F12-1)</f>
         <v/>
       </c>
@@ -19881,7 +22490,7 @@
         <f>SUM(D16:D19)</f>
         <v/>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="29">
         <f>IF(B20=0,"",C20/B20-1)</f>
         <v/>
       </c>
@@ -22814,7 +25423,7 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
@@ -25166,7 +27775,7 @@
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
@@ -27182,7 +29791,7 @@
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
@@ -37206,7 +39815,7 @@
       </c>
       <c r="D311" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E311" s="10" t="inlineStr">
@@ -37262,7 +39871,7 @@
       </c>
       <c r="D312" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E312" s="10" t="inlineStr">
@@ -37318,7 +39927,7 @@
       </c>
       <c r="D313" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E313" s="10" t="inlineStr">
@@ -37374,7 +39983,7 @@
       </c>
       <c r="D314" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E314" s="10" t="inlineStr">
@@ -37430,7 +40039,7 @@
       </c>
       <c r="D315" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E315" s="10" t="inlineStr">
@@ -37486,7 +40095,7 @@
       </c>
       <c r="D316" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E316" s="10" t="inlineStr">
@@ -38102,7 +40711,7 @@
       </c>
       <c r="D327" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E327" s="10" t="inlineStr">
@@ -48294,7 +50903,7 @@
       </c>
       <c r="D509" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E509" s="10" t="inlineStr">
@@ -48350,7 +50959,7 @@
       </c>
       <c r="D510" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E510" s="10" t="inlineStr">
@@ -51206,7 +53815,7 @@
       </c>
       <c r="D561" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E561" s="10" t="inlineStr">
@@ -58990,7 +61599,7 @@
       </c>
       <c r="D700" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E700" s="10" t="inlineStr">
@@ -59158,7 +61767,7 @@
       </c>
       <c r="D703" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E703" s="10" t="inlineStr">
@@ -65710,7 +68319,7 @@
       </c>
       <c r="D820" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E820" s="10" t="inlineStr">
@@ -67558,7 +70167,7 @@
       </c>
       <c r="D853" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E853" s="10" t="inlineStr">
@@ -68006,7 +70615,7 @@
       </c>
       <c r="D861" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E861" s="10" t="inlineStr">
@@ -68118,7 +70727,7 @@
       </c>
       <c r="D863" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E863" s="10" t="inlineStr">
@@ -68566,7 +71175,7 @@
       </c>
       <c r="D871" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E871" s="10" t="inlineStr">
